--- a/FLORES DE ESTRADA/Agosto/RESUMEN-Agosto-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Agosto/RESUMEN-Agosto-ESTRADA.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\FLORES DE ESTRADA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A06D3B8-8B45-490D-90C5-9FF359C35A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84C079A-1BC2-4C0F-9780-5B9B347A015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -132,28 +132,31 @@
     <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
   </si>
   <si>
-    <t>AYSA - JULIO 2025</t>
-  </si>
-  <si>
-    <t>ASCENSORES Premec S.R.L. - Mantenimiento de Ascensor JULIO</t>
-  </si>
-  <si>
-    <t>Administraciòn JULIO 2025:</t>
-  </si>
-  <si>
-    <t>Egresos gastos del mes - JULIO ORDINARIO</t>
-  </si>
-  <si>
-    <t>Egresos gastos del mes - JULIO EXTRAORDINARIO</t>
-  </si>
-  <si>
-    <t>PERIODO: JULIO - Vto. 14/08</t>
-  </si>
-  <si>
     <t>SUELDO SRA. FERNANDA</t>
   </si>
   <si>
     <t>AUMENTARON LOS HONORARIOS EN JULI 2025</t>
+  </si>
+  <si>
+    <t>PERIODO: AGOSTO - Vto. 15/09</t>
+  </si>
+  <si>
+    <t>AYSA - AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>ASCENSORES Premec S.R.L. - Mantenimiento de Ascensor AGOSTO</t>
+  </si>
+  <si>
+    <t>Administraciòn AGOSTO 2025:</t>
+  </si>
+  <si>
+    <t>Egresos gastos del mes - AGOSTO ORDINARIO</t>
+  </si>
+  <si>
+    <t>Egresos gastos del mes - AGOSTO EXTRAORDINARIO</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
   </si>
 </sst>
 </file>
@@ -161,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -445,13 +448,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -466,20 +469,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -489,11 +492,27 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -512,28 +531,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -871,16 +882,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="25"/>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -890,7 +901,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="23"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -904,7 +915,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -918,7 +929,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -932,7 +943,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="23"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -944,7 +955,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -954,7 +965,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="s">
         <v>5</v>
       </c>
@@ -962,13 +973,13 @@
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="E7" s="31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="32"/>
       <c r="H7" s="33"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="25"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -978,7 +989,7 @@
       <c r="G8" s="26"/>
       <c r="H8" s="27"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>6</v>
       </c>
@@ -992,7 +1003,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>8</v>
       </c>
@@ -1006,7 +1017,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1016,182 +1027,182 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44">
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="62">
         <v>218000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="44"/>
-    </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47">
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40">
         <f>SUM(H13:H14)</f>
         <v>218000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="51">
-        <v>29693.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="46" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="61">
+        <v>29691.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="48">
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="41">
         <f>SUM(H17:H17)</f>
-        <v>29693.32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+        <v>29691.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="51">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="44">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="52">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="45">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="51">
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="44">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
-        <v>12</v>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="60" t="s">
+        <v>42</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -1199,118 +1210,117 @@
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
       <c r="G25" s="46"/>
-      <c r="H25" s="48">
-        <f>SUM(H24:H24)</f>
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
+      <c r="H25" s="61">
+        <f>96180+40150</f>
+        <v>136330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="41">
+        <f>SUM(H24:H25)</f>
+        <v>206330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="43" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43" t="s">
+      <c r="B28" s="37"/>
+      <c r="C28" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43" t="s">
+      <c r="D28" s="37"/>
+      <c r="E28" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="21"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="54">
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="47">
         <v>148100</v>
       </c>
-      <c r="I28" s="21"/>
-      <c r="K28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="42" t="s">
+      <c r="I29" s="21"/>
+      <c r="K29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="43" t="s">
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="13">
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="13">
         <v>49773</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="55" t="s">
+    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="56">
-        <f>H30+H28+H25+H22+H18+H15</f>
-        <v>515566.32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="49">
+        <f>H31+H29+H26+H22+H18+H15</f>
+        <v>651894.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="35" t="s">
         <v>32</v>
-      </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="36">
-        <v>786634.68</v>
-      </c>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>29</v>
       </c>
       <c r="B33" s="35"/>
       <c r="C33" s="35"/>
@@ -1319,98 +1329,100 @@
       <c r="F33" s="35"/>
       <c r="G33" s="35"/>
       <c r="H33" s="36">
-        <f>H31+H32</f>
-        <v>1302201</v>
-      </c>
-      <c r="I33" s="24"/>
-    </row>
-    <row r="34" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="str">
+        <v>786634.68</v>
+      </c>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36">
+        <f>H32+H33</f>
+        <v>1438529.08</v>
+      </c>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="59" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B34" s="57"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="34"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="34"/>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="41"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A39" s="53"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="55"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="17">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="17">
         <v>2636101.4531489071</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="19">
-        <v>1341031.5093240894</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1418,15 +1430,13 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
-      <c r="H41" s="58">
-        <f>-12057-5988.47</f>
-        <v>-18045.47</v>
-      </c>
-      <c r="I41" s="20"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H41" s="19">
+        <v>1341031.5093240894</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1434,14 +1444,15 @@
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
-      <c r="H42" s="14">
-        <f>-( H31 )</f>
-        <v>-515566.32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H42" s="50">
+        <f>-12057-5988.47</f>
+        <v>-18045.47</v>
+      </c>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1449,109 +1460,124 @@
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
-      <c r="H43" s="14"/>
-    </row>
-    <row r="44" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="H43" s="14">
+        <f>-( H32 )</f>
+        <v>-651894.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A45" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="18">
-        <f>SUM(H39:H43)</f>
-        <v>3443521.1724729966</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="18">
+        <f>SUM(H40:H44)</f>
+        <v>3307193.0924729966</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
       <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B46:G51"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="B47:G52"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/FLORES DE ESTRADA/Agosto/RESUMEN-Agosto-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Agosto/RESUMEN-Agosto-ESTRADA.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\FLORES DE ESTRADA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84C079A-1BC2-4C0F-9780-5B9B347A015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093C89EC-556E-41E2-A3F2-FA4CA9B335C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$54</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Arreglo lingas porton - 20mts de cable - mano de obra y colocacion</t>
   </si>
 </sst>
 </file>
@@ -164,10 +167,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -448,13 +451,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -469,20 +472,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -492,27 +495,30 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -540,11 +546,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -882,16 +883,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="25"/>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -901,7 +902,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="23"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -915,7 +916,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -929,7 +930,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -943,7 +944,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -955,7 +956,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -965,7 +966,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
         <v>5</v>
       </c>
@@ -979,7 +980,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="33"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -989,7 +990,7 @@
       <c r="G8" s="26"/>
       <c r="H8" s="27"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>6</v>
       </c>
@@ -1003,7 +1004,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>8</v>
       </c>
@@ -1017,7 +1018,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1027,19 +1028,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="56" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
         <v>34</v>
       </c>
@@ -1049,21 +1050,21 @@
       <c r="E13" s="37"/>
       <c r="F13" s="37"/>
       <c r="G13" s="37"/>
-      <c r="H13" s="62">
+      <c r="H13" s="38">
         <v>218000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="H14" s="38"/>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
         <v>9</v>
       </c>
@@ -1078,19 +1079,19 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="56" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
         <v>37</v>
       </c>
@@ -1100,11 +1101,11 @@
       <c r="E17" s="37"/>
       <c r="F17" s="37"/>
       <c r="G17" s="37"/>
-      <c r="H17" s="61">
-        <v>29691.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H17" s="44">
+        <v>29397.43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
         <v>11</v>
       </c>
@@ -1116,22 +1117,22 @@
       <c r="G18" s="39"/>
       <c r="H18" s="41">
         <f>SUM(H17:H17)</f>
-        <v>29691.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="56" t="s">
+        <v>29397.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
         <v>20</v>
       </c>
@@ -1145,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
         <v>30</v>
       </c>
@@ -1159,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
         <v>9</v>
       </c>
@@ -1174,35 +1175,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="56" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="58" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
       <c r="H24" s="44">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="60" t="s">
-        <v>42</v>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
+        <v>43</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -1210,133 +1211,131 @@
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
       <c r="G25" s="46"/>
-      <c r="H25" s="61">
+      <c r="H25" s="44">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="44">
         <f>96180+40150</f>
         <v>136330</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39" t="s">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="41">
-        <f>SUM(H24:H25)</f>
-        <v>206330</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="56" t="s">
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="41">
+        <f>SUM(H24:H26)</f>
+        <v>406330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="37" t="s">
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37" t="s">
+      <c r="B29" s="37"/>
+      <c r="C29" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37" t="s">
+      <c r="D29" s="37"/>
+      <c r="E29" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="21"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="39" t="s">
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="21"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="47">
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="47">
         <v>148100</v>
       </c>
-      <c r="I29" s="21"/>
-      <c r="K29" t="s">
+      <c r="I30" s="21"/>
+      <c r="K30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="56" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="37" t="s">
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="13">
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="13">
         <v>49773</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="48" t="s">
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49">
-        <f>H31+H29+H26+H22+H18+H15</f>
-        <v>651894.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="35" t="s">
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="49">
+        <f>H32+H30+H27+H22+H18+H15</f>
+        <v>851600.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="35" t="s">
         <v>32</v>
-      </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="36">
-        <v>786634.68</v>
-      </c>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="s">
-        <v>29</v>
       </c>
       <c r="B34" s="35"/>
       <c r="C34" s="35"/>
@@ -1345,98 +1344,101 @@
       <c r="F34" s="35"/>
       <c r="G34" s="35"/>
       <c r="H34" s="36">
-        <f>H32+H33</f>
-        <v>1438529.08</v>
-      </c>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="59" t="str">
+        <f>1302201-851600</f>
+        <v>450601</v>
+      </c>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="36">
+        <f>H33+H34</f>
+        <v>1302201.4300000002</v>
+      </c>
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="60" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B35" s="59"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="34"/>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="52" t="s">
+      <c r="B36" s="60"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="34"/>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-    </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="55"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="s">
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="53"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="54"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="56"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="17">
-        <v>2636101.4531489071</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="17">
+        <v>3443521.1724729966</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="19">
-        <v>1341031.5093240894</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1444,15 +1446,13 @@
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
-      <c r="H42" s="50">
-        <f>-12057-5988.47</f>
-        <v>-18045.47</v>
-      </c>
-      <c r="I42" s="20"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H42" s="19">
+        <v>1554639.1810947841</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1460,14 +1460,15 @@
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
-      <c r="H43" s="14">
-        <f>-( H32 )</f>
-        <v>-651894.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H43" s="50">
+        <f>-12057-5988.47</f>
+        <v>-18045.47</v>
+      </c>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1475,109 +1476,124 @@
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="14"/>
-    </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A45" s="15" t="s">
+      <c r="H44" s="14">
+        <f>-( H33 )</f>
+        <v>-851600.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="18">
-        <f>SUM(H40:H44)</f>
-        <v>3307193.0924729966</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="18">
+        <f>SUM(H41:H45)</f>
+        <v>4128514.453567781</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
+      <c r="B48" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
       <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="8"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B47:G52"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="B48:G53"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
